--- a/luaran/templates/tables/Table5_Stages_Classification.xlsx
+++ b/luaran/templates/tables/Table5_Stages_Classification.xlsx
@@ -461,14 +461,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -476,6 +476,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,80 +492,87 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Training
+Time (min)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Accuracy</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Balanced Acc</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ring (n=259)</t>
         </is>
       </c>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Trophozoite (n=14)</t>
         </is>
       </c>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Schizont (n=6)</t>
         </is>
       </c>
-      <c r="J1" s="2" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Gametocyte (n=5)</t>
         </is>
       </c>
-      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="2" t="n"/>
       <c r="D2" s="2" t="n"/>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -579,34 +587,37 @@
       <c r="B3" s="5" t="n">
         <v>25.6</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D3" s="6" t="n">
         <v>0.9612999999999999</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="E3" s="6" t="n">
         <v>0.8304</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="F3" s="6" t="n">
         <v>0.9808</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="G3" s="6" t="n">
         <v>0.9846</v>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="H3" s="6" t="n">
         <v>0.7778</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="I3" s="6" t="n">
         <v>0.6087</v>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="J3" s="6" t="n">
         <v>0.625</v>
       </c>
-      <c r="J3" s="6" t="n">
+      <c r="K3" s="6" t="n">
         <v>0.7143</v>
       </c>
-      <c r="K3" s="6" t="n">
+      <c r="L3" s="6" t="n">
         <v>0.8333</v>
       </c>
-      <c r="L3" s="6" t="n">
+      <c r="M3" s="6" t="n">
         <v>0.9091</v>
       </c>
     </row>
@@ -619,34 +630,37 @@
       <c r="B4" s="5" t="n">
         <v>7.8</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>0.9542</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>0.7864</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="F4" s="6" t="n">
         <v>0.9808</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>0.9846</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="H4" s="6" t="n">
         <v>0.7143</v>
       </c>
-      <c r="H4" s="6" t="n">
+      <c r="I4" s="6" t="n">
         <v>0.4762</v>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="J4" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="J4" s="6" t="n">
+      <c r="K4" s="6" t="n">
         <v>0.75</v>
       </c>
-      <c r="K4" s="6" t="n">
+      <c r="L4" s="6" t="n">
         <v>0.6667</v>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="M4" s="6" t="n">
         <v>0.7272999999999999</v>
       </c>
     </row>
@@ -659,34 +673,37 @@
       <c r="B5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>0.9437000000000001</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.6698999999999999</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="F5" s="6" t="n">
         <v>0.9808</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="G5" s="6" t="n">
         <v>0.9827</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="H5" s="6" t="n">
         <v>0.5455</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="I5" s="6" t="n">
         <v>0.48</v>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="J5" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="K5" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="K5" s="6" t="n">
+      <c r="L5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="M5" s="6" t="n">
         <v>0.75</v>
       </c>
     </row>
@@ -699,34 +716,37 @@
       <c r="B6" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>0.9472</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="E6" s="6" t="n">
         <v>0.7031000000000001</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="F6" s="6" t="n">
         <v>0.9771</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="G6" s="6" t="n">
         <v>0.9827</v>
       </c>
-      <c r="G6" s="6" t="n">
+      <c r="H6" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="H6" s="6" t="n">
+      <c r="I6" s="6" t="n">
         <v>0.4167</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="J6" s="6" t="n">
         <v>0.5714</v>
       </c>
-      <c r="J6" s="6" t="n">
+      <c r="K6" s="6" t="n">
         <v>0.6153999999999999</v>
       </c>
-      <c r="K6" s="6" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="L6" s="6" t="n">
+      <c r="M6" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
@@ -739,34 +759,37 @@
       <c r="B7" s="5" t="n">
         <v>44.5</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>0.9506999999999999</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="E7" s="6" t="n">
         <v>0.7056999999999999</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="F7" s="6" t="n">
         <v>0.9808</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="G7" s="6" t="n">
         <v>0.9827</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>0.5714</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>0.5714</v>
       </c>
       <c r="I7" s="6" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="J7" s="6" t="n">
         <v>0.8</v>
       </c>
-      <c r="J7" s="6" t="n">
+      <c r="K7" s="6" t="n">
         <v>0.7272999999999999</v>
       </c>
-      <c r="K7" s="6" t="n">
+      <c r="L7" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="L7" s="6" t="n">
+      <c r="M7" s="6" t="n">
         <v>0.6</v>
       </c>
     </row>
@@ -779,46 +802,50 @@
       <c r="B8" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>0.9225</v>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="E8" s="6" t="n">
         <v>0.7791</v>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.9801</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="G8" s="6" t="n">
         <v>0.9647</v>
       </c>
-      <c r="G8" s="6" t="n">
+      <c r="H8" s="6" t="n">
         <v>0.4667</v>
       </c>
-      <c r="H8" s="6" t="n">
+      <c r="I8" s="6" t="n">
         <v>0.4828</v>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="J8" s="6" t="n">
         <v>0.3333</v>
       </c>
-      <c r="J8" s="6" t="n">
+      <c r="K8" s="6" t="n">
         <v>0.4444</v>
       </c>
-      <c r="K8" s="6" t="n">
+      <c r="L8" s="6" t="n">
         <v>0.8333</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="M8" s="6" t="n">
         <v>0.9091</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="K1:L1"/>
+  <mergeCells count="9">
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:G1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luaran/templates/tables/Table5_Stages_Classification.xlsx
+++ b/luaran/templates/tables/Table5_Stages_Classification.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MP-IDB Stages" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MP-IDB Stages" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
